--- a/docpin_differences.xlsx
+++ b/docpin_differences.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="140">
   <si>
     <t xml:space="preserve">tage</t>
   </si>
@@ -163,6 +163,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">document_chunker_patch.py</t>
     </r>
@@ -171,6 +172,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> introduces chunk_text_hybrid() which fixes this: it detects Markdown table lines (regex </t>
     </r>
@@ -180,6 +182,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">^\s*\|</t>
     </r>
@@ -188,6 +191,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">) and emits the entire table as one atomic chunk. Prose is still processed by the original chunker.</t>
     </r>
@@ -196,129 +200,328 @@
     <t xml:space="preserve">3. Embedding &amp; Storage</t>
   </si>
   <si>
+    <t xml:space="preserve">Chunks are stored as plain text in PostgreSQL's chunks.content column, with a 384-dim vector from all-MiniLM-L6-v2. The embedding model has a 512-token hard limit — for large tables, only the header + top rows are captured in the vector; the rest of the table is invisible to semantic search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Retrieval (RRF Hybrid Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector search: finds the right table via its header (semantic match)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM25 keyword search: searches the full stored Markdown text (catches specific row values)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both signals are fused via RRF (k=60), then top-k chunks returned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Context Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retrieved chunks are wrapped in XML &lt;chunk id='N'&gt; elements. The full Markdown table is passed as-is to the LLM — no pre-computation of cell values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Why G3 (Arithmetic) = 0% and Why G2 is Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root Cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3 = 0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires multi-step arithmetic (e.g. subtract two table cells). The LLM must parse Markdown delimiters, locate two values, and compute — too complex for 4B–7B models; all models tested return N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2 = 50% num_match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terse field names ("Product", "Service and other") map to multiple table rows across time periods; without column/row disambiguation the model picks the wrong cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedding truncation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tables &gt;512 tokens have their lower rows invisible to vector search; a needed value in row 20+ may never be retrieved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potential Improvements Not Yet Implemented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structured table extraction: Post-process Markdown tables into typed JSON ({"commercial_paper": {"fair_value": 9044}}) before storing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larger embedding context: Switch to nomic-embed-text-v1.5 (8K token window) to fully encode large financial tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-step prompting: Have the LLM first extract values, then compute — rather than doing both in one shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stronger model: G3 arithmetic failures are model-capacity issues; DeepSeek V4 Pro and Gemma-31B still return N/A for all 30 G3 questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek V4 Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek V4 Flash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">think, chunks50, top10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-5 nano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemma4 31B Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">think, top20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemma4-E4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4o-mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nodatefilter, top20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude-opus-4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemma4-4B Q4 K M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemma4-31B Q4 K M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full docx, char-chunked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB chunks from docling parse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chunk selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lexical (exact field name match)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semantic/RRF (concept match)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 102 chunks ranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-10 from 60 doc chunks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thinking mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A rate G2/G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ablation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chunks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NumMatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_markdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docling MD char-window 2200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_hybrid (5000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docling MD, whole-table + RecursiveChunker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">context_source v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docling natural segs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCX XML char-window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_hybrid (2200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">And at runtime: max_seq_length = 256 — so the old pipeline uses 256 subword tokens (WordPiece from all-MiniLM-L6-v2), not characters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In raw characters, 256 WordPiece tokens of financial Markdown text is roughly 800–1200 chars. That's what produced the 1211-chunk result and the terrible 37% score — the chunks were far too small to contain a full financial table row with its header context.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Chunks are stored as plain text in PostgreSQL's </t>
+      <t xml:space="preserve">So the old pipeline's chunk size is conceptually between our table_hybrid (256 chars) (too small) and table_hybrid (2200 chars) (already much better), but measured in a token unit that maps to ~1000 chars. The </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">chunks.content</t>
+      <t xml:space="preserve">document_chunker_patch.py</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> column, with a 384-dim vector from all-MiniLM-L6-v2. The embedding model has a 512-token hard limit — for large tables, only the header + top rows are captured in the vector; the rest of the table is invisible to semantic search.</t>
+      <t xml:space="preserve"> was written specifically to work around this — it sidesteps the 256-token limit for tables by keeping them whole and only applying the RecursiveChunker to prose</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Retrieval (RRF Hybrid Search)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vector search: finds the right table via its header (semantic match)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BM25 keyword search: searches the full stored Markdown text (catches specific row values)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both signals are fused via RRF (k=60), then top-k chunks returned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Context Assembly</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Retrieved chunks are wrapped in XML </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;chunk id='N'&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> elements. The full Markdown table is passed as-is to the LLM — no pre-computation of cell values.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Why G3 (Arithmetic) = 0% and Why G2 is Hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root Cause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G3 = 0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires multi-step arithmetic (e.g. subtract two table cells). The LLM must parse Markdown delimiters, locate two values, and compute — too complex for 4B–7B models; all models tested return N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G2 = 50% num_match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terse field names ("Product", "Service and other") map to multiple table rows across time periods; without column/row disambiguation the model picks the wrong cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embedding truncation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tables &gt;512 tokens have their lower rows invisible to vector search; a needed value in row 20+ may never be retrieved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potential Improvements Not Yet Implemented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structured table extraction: Post-process Markdown tables into typed JSON ({"commercial_paper": {"fair_value": 9044}}) before storing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larger embedding context: Switch to nomic-embed-text-v1.5 (8K token window) to fully encode large financial tables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-step prompting: Have the LLM first extract values, then compute — rather than doing both in one shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stronger model: G3 arithmetic failures are model-capacity issues; DeepSeek V4 Pro and Gemma-31B still return N/A for all 30 G3 questions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -340,29 +543,55 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="16"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -407,33 +636,93 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -559,311 +848,745 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultColWidth="32.96484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="59.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="47.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="4"/>
+      <c r="B18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="6"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="5"/>
+      <c r="B27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="5"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="3"/>
+      <c r="B32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="5"/>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="5"/>
+      <c r="B38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42" s="10"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="15" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C65" s="14" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="20" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="E86" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D87" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E87" s="21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>615</v>
+      </c>
+      <c r="D88" s="20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E88" s="21" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>615</v>
+      </c>
+      <c r="D89" s="20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E89" s="21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D90" s="20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E90" s="21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E91" s="21" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92" s="20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F92" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="16" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -890,8 +1613,9 @@
     <mergeCell ref="A42:B42"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" display="chunks.content"/>
-    <hyperlink ref="A32" r:id="rId2" display="&lt;chunk id='N'&gt;"/>
+    <hyperlink ref="A26" r:id="rId1" display="Chunks are stored as plain text in PostgreSQL's chunks.content column, with a 384-dim vector from all-MiniLM-L6-v2. The embedding model has a 512-token hard limit — for large tables, only the header + top rows are captured in the vector; the rest of the table is invisible to semantic search."/>
+    <hyperlink ref="A32" r:id="rId2" display="Retrieved chunks are wrapped in XML &lt;chunk id='N'&gt; elements. The full Markdown table is passed as-is to the LLM — no pre-computation of cell values."/>
+    <hyperlink ref="A98" r:id="rId3" display="document_chunker_patch.py"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
